--- a/docs/template/summary.xlsx
+++ b/docs/template/summary.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/restupriyono/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6274C4-3184-4548-9263-415D42EEF212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -32,219 +27,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={952B16D3-B9CB-5344-94E4-09DA14C8D996}</author>
-    <author>tc={6690882D-83AE-4F49-AEA3-359933E838B6}</author>
-    <author>tc={306182D7-635D-AE43-8391-AE8BAF008B64}</author>
-    <author>tc={ED23E3CF-0195-5348-A86D-AB6D663010FB}</author>
-    <author>tc={1926CF56-FAB1-9F4F-A7CD-8366012E27A0}</author>
-    <author>tc={95184178-802D-B345-B1D8-5375EB49E7A1}</author>
-    <author>tc={903E833A-88A4-5D46-A612-23C625415198}</author>
-    <author>tc={4F96DB87-518E-E142-97BF-31275CEDEA7B}</author>
-    <author>tc={52E9E1DA-300F-8D43-AC9C-B5053804AADA}</author>
-    <author>tc={8A48D25F-E8B1-8D42-B1AA-6E0624B6E93D}</author>
-    <author>tc={C5F13C2E-400B-9B4C-9226-88092E6A2E86}</author>
-    <author>tc={1A4FBA55-6B42-C846-9F63-4250D577F01A}</author>
-  </authors>
-  <commentList>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    zramadhan
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C6" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    hanif
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C7" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    dewani
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C8" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    herlan
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C9" authorId="4" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    hasan
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C10" authorId="5" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    rahmat
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="6" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    fathir
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="7" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    sagara
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C13" authorId="8" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    alkahfi
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C14" authorId="9" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    mulya
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C15" authorId="10" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    daus
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C16" authorId="11" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    pilihan
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3358,7 +3140,6 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/docs/template/summary.xlsx
+++ b/docs/template/summary.xlsx
@@ -3,7 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6274C4-3184-4548-9263-415D42EEF212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/restupriyono/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73FA6D2-4BBD-0842-979B-FDC89C355B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +189,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(&quot;IDR&quot;* #,##0_);_(&quot;IDR&quot;* \(#,##0\);_(&quot;IDR&quot;* \-_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -206,11 +211,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -341,9 +341,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -354,10 +354,67 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -369,67 +426,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -693,2051 +690,2057 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DI22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="6.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="4.6640625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" style="9" customWidth="1"/>
-    <col min="5" max="11" width="5.83203125" style="9" customWidth="1"/>
-    <col min="12" max="19" width="6.5" style="9"/>
-    <col min="20" max="23" width="5.6640625" style="9" customWidth="1"/>
-    <col min="24" max="24" width="8.6640625" style="9" customWidth="1"/>
-    <col min="25" max="25" width="5.6640625" style="9" customWidth="1"/>
-    <col min="26" max="26" width="13" style="9" customWidth="1"/>
-    <col min="27" max="27" width="11.6640625" style="9" customWidth="1"/>
-    <col min="28" max="28" width="13" style="9" customWidth="1"/>
-    <col min="29" max="31" width="11.6640625" style="9" customWidth="1"/>
-    <col min="32" max="32" width="12.1640625" style="9" customWidth="1"/>
-    <col min="33" max="33" width="11.6640625" style="9" customWidth="1"/>
-    <col min="114" max="16304" width="6.5" style="9"/>
-    <col min="16305" max="16384" width="10.5" style="9" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="4.6640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" style="5" customWidth="1"/>
+    <col min="5" max="11" width="5.83203125" style="5" customWidth="1"/>
+    <col min="12" max="19" width="6.5" style="5"/>
+    <col min="20" max="23" width="5.6640625" style="5" customWidth="1"/>
+    <col min="24" max="24" width="8.6640625" style="5" customWidth="1"/>
+    <col min="25" max="25" width="5.6640625" style="5" customWidth="1"/>
+    <col min="26" max="26" width="13" style="5" customWidth="1"/>
+    <col min="27" max="27" width="11.6640625" style="5" customWidth="1"/>
+    <col min="28" max="28" width="13" style="5" customWidth="1"/>
+    <col min="29" max="31" width="11.6640625" style="5" customWidth="1"/>
+    <col min="32" max="32" width="12.1640625" style="5" customWidth="1"/>
+    <col min="33" max="33" width="11.6640625" style="5" customWidth="1"/>
+    <col min="114" max="16304" width="6.5" style="5"/>
+    <col min="16305" max="16384" width="10.5" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="7"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="7"/>
     </row>
     <row r="2" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7" t="s">
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7" t="s">
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="U2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="12" t="s">
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="Y2" s="7" t="s">
+      <c r="Y2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="Z2" s="7" t="s">
+      <c r="Z2" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7" t="s">
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="6" t="s">
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="AE2" s="5" t="s">
+      <c r="AE2" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="21"/>
     </row>
     <row r="3" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7" t="s">
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7" t="s">
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="V3" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="W3" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="X3" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="6" t="s">
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AA3" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AB3" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="AC3" s="7" t="s">
+      <c r="AC3" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="4" t="s">
+      <c r="AD3" s="25"/>
+      <c r="AE3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AF3" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="AG3" s="5" t="s">
+      <c r="AG3" s="21" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="12" t="s">
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="12" t="s">
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="P4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="12" t="s">
+      <c r="Q4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="R4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="S4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="7"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="4"/>
-      <c r="AG4" s="5"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+      <c r="V4" s="26"/>
+      <c r="W4" s="26"/>
+      <c r="X4" s="26"/>
+      <c r="Y4" s="26"/>
+      <c r="Z4" s="25"/>
+      <c r="AA4" s="26"/>
+      <c r="AB4" s="25"/>
+      <c r="AC4" s="26"/>
+      <c r="AD4" s="25"/>
+      <c r="AE4" s="20"/>
+      <c r="AF4" s="20"/>
+      <c r="AG4" s="21"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A5" s="13">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="22">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="14">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14">
-        <v>0</v>
-      </c>
-      <c r="H5" s="14">
-        <v>0</v>
-      </c>
-      <c r="I5" s="14">
-        <v>0</v>
-      </c>
-      <c r="J5" s="14">
-        <v>0</v>
-      </c>
-      <c r="K5" s="14">
-        <v>0</v>
-      </c>
-      <c r="L5" s="14">
-        <v>0</v>
-      </c>
-      <c r="M5" s="14">
-        <v>0</v>
-      </c>
-      <c r="N5" s="14">
-        <v>0</v>
-      </c>
-      <c r="O5" s="14">
-        <v>0</v>
-      </c>
-      <c r="P5" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>0</v>
-      </c>
-      <c r="R5" s="14">
-        <v>0</v>
-      </c>
-      <c r="S5" s="14">
-        <v>0</v>
-      </c>
-      <c r="T5" s="14">
+      <c r="D5" s="8">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0</v>
+      </c>
+      <c r="S5" s="8">
+        <v>0</v>
+      </c>
+      <c r="T5" s="8">
         <f t="shared" ref="T5:T18" si="0">G5+N5</f>
         <v>0</v>
       </c>
-      <c r="U5" s="14">
-        <v>0</v>
-      </c>
-      <c r="V5" s="14">
-        <v>0</v>
-      </c>
-      <c r="W5" s="14">
-        <v>0</v>
-      </c>
-      <c r="X5" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="15">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="15">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="15">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="15">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="16">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="16">
+      <c r="U5" s="8">
+        <v>0</v>
+      </c>
+      <c r="V5" s="8">
+        <v>0</v>
+      </c>
+      <c r="W5" s="8">
+        <v>0</v>
+      </c>
+      <c r="X5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A6" s="13">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="22"/>
+      <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="14">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14">
-        <v>0</v>
-      </c>
-      <c r="H6" s="14">
-        <v>0</v>
-      </c>
-      <c r="I6" s="14">
-        <v>0</v>
-      </c>
-      <c r="J6" s="14">
-        <v>0</v>
-      </c>
-      <c r="K6" s="14">
-        <v>0</v>
-      </c>
-      <c r="L6" s="14">
-        <v>0</v>
-      </c>
-      <c r="M6" s="14">
-        <v>0</v>
-      </c>
-      <c r="N6" s="14">
-        <v>0</v>
-      </c>
-      <c r="O6" s="14">
-        <v>0</v>
-      </c>
-      <c r="P6" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>0</v>
-      </c>
-      <c r="R6" s="14">
-        <v>0</v>
-      </c>
-      <c r="S6" s="14">
-        <v>0</v>
-      </c>
-      <c r="T6" s="14">
+      <c r="D6" s="8">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
+      <c r="N6" s="8">
+        <v>0</v>
+      </c>
+      <c r="O6" s="8">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
+        <v>0</v>
+      </c>
+      <c r="S6" s="8">
+        <v>0</v>
+      </c>
+      <c r="T6" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U6" s="14">
-        <v>0</v>
-      </c>
-      <c r="V6" s="14">
-        <v>0</v>
-      </c>
-      <c r="W6" s="14">
-        <v>0</v>
-      </c>
-      <c r="X6" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="15">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="15">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="15">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="15">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="16">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="16">
+      <c r="U6" s="8">
+        <v>0</v>
+      </c>
+      <c r="V6" s="8">
+        <v>0</v>
+      </c>
+      <c r="W6" s="8">
+        <v>0</v>
+      </c>
+      <c r="X6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A7" s="13">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="22"/>
+      <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="14">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14">
-        <v>0</v>
-      </c>
-      <c r="H7" s="14">
-        <v>0</v>
-      </c>
-      <c r="I7" s="14">
-        <v>0</v>
-      </c>
-      <c r="J7" s="14">
-        <v>0</v>
-      </c>
-      <c r="K7" s="14">
-        <v>0</v>
-      </c>
-      <c r="L7" s="14">
-        <v>0</v>
-      </c>
-      <c r="M7" s="14">
-        <v>0</v>
-      </c>
-      <c r="N7" s="14">
-        <v>0</v>
-      </c>
-      <c r="O7" s="14">
-        <v>0</v>
-      </c>
-      <c r="P7" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="14">
-        <v>0</v>
-      </c>
-      <c r="R7" s="14">
-        <v>0</v>
-      </c>
-      <c r="S7" s="14">
-        <v>0</v>
-      </c>
-      <c r="T7" s="14">
+      <c r="D7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+      <c r="O7" s="8">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
+        <v>0</v>
+      </c>
+      <c r="S7" s="8">
+        <v>0</v>
+      </c>
+      <c r="T7" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U7" s="14">
-        <v>0</v>
-      </c>
-      <c r="V7" s="14">
-        <v>0</v>
-      </c>
-      <c r="W7" s="14">
-        <v>0</v>
-      </c>
-      <c r="X7" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="15">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="15">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="15">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="15">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="16">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="16">
+      <c r="U7" s="8">
+        <v>0</v>
+      </c>
+      <c r="V7" s="8">
+        <v>0</v>
+      </c>
+      <c r="W7" s="8">
+        <v>0</v>
+      </c>
+      <c r="X7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A8" s="17">
+      <c r="A8" s="2">
         <v>3</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="23">
         <v>2</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="18">
-        <v>0</v>
-      </c>
-      <c r="E8" s="18">
-        <v>0</v>
-      </c>
-      <c r="F8" s="18">
-        <v>0</v>
-      </c>
-      <c r="G8" s="18">
-        <v>0</v>
-      </c>
-      <c r="H8" s="18">
-        <v>0</v>
-      </c>
-      <c r="I8" s="18">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18">
-        <v>0</v>
-      </c>
-      <c r="M8" s="18">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18">
-        <v>0</v>
-      </c>
-      <c r="P8" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="18">
-        <v>0</v>
-      </c>
-      <c r="R8" s="18">
-        <v>0</v>
-      </c>
-      <c r="S8" s="18">
-        <v>0</v>
-      </c>
-      <c r="T8" s="18">
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0</v>
+      </c>
+      <c r="K8" s="11">
+        <v>0</v>
+      </c>
+      <c r="L8" s="11">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11">
+        <v>0</v>
+      </c>
+      <c r="N8" s="11">
+        <v>0</v>
+      </c>
+      <c r="O8" s="11">
+        <v>0</v>
+      </c>
+      <c r="P8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>0</v>
+      </c>
+      <c r="T8" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U8" s="18">
-        <v>0</v>
-      </c>
-      <c r="V8" s="18">
-        <v>0</v>
-      </c>
-      <c r="W8" s="18">
-        <v>0</v>
-      </c>
-      <c r="X8" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="19">
+      <c r="U8" s="11">
+        <v>0</v>
+      </c>
+      <c r="V8" s="11">
+        <v>0</v>
+      </c>
+      <c r="W8" s="11">
+        <v>0</v>
+      </c>
+      <c r="X8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A9" s="17">
+      <c r="A9" s="2">
         <v>4</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="23"/>
+      <c r="C9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="18">
-        <v>0</v>
-      </c>
-      <c r="E9" s="18">
-        <v>0</v>
-      </c>
-      <c r="F9" s="18">
-        <v>0</v>
-      </c>
-      <c r="G9" s="18">
-        <v>0</v>
-      </c>
-      <c r="H9" s="18">
-        <v>0</v>
-      </c>
-      <c r="I9" s="18">
-        <v>0</v>
-      </c>
-      <c r="J9" s="18">
-        <v>0</v>
-      </c>
-      <c r="K9" s="18">
-        <v>0</v>
-      </c>
-      <c r="L9" s="18">
-        <v>0</v>
-      </c>
-      <c r="M9" s="18">
-        <v>0</v>
-      </c>
-      <c r="N9" s="18">
-        <v>0</v>
-      </c>
-      <c r="O9" s="18">
-        <v>0</v>
-      </c>
-      <c r="P9" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>0</v>
-      </c>
-      <c r="R9" s="18">
-        <v>0</v>
-      </c>
-      <c r="S9" s="18">
-        <v>0</v>
-      </c>
-      <c r="T9" s="18">
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0</v>
+      </c>
+      <c r="J9" s="11">
+        <v>0</v>
+      </c>
+      <c r="K9" s="11">
+        <v>0</v>
+      </c>
+      <c r="L9" s="11">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11">
+        <v>0</v>
+      </c>
+      <c r="N9" s="11">
+        <v>0</v>
+      </c>
+      <c r="O9" s="11">
+        <v>0</v>
+      </c>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>0</v>
+      </c>
+      <c r="T9" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U9" s="18">
-        <v>0</v>
-      </c>
-      <c r="V9" s="18">
-        <v>0</v>
-      </c>
-      <c r="W9" s="18">
-        <v>0</v>
-      </c>
-      <c r="X9" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="19">
+      <c r="U9" s="11">
+        <v>0</v>
+      </c>
+      <c r="V9" s="11">
+        <v>0</v>
+      </c>
+      <c r="W9" s="11">
+        <v>0</v>
+      </c>
+      <c r="X9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A10" s="17">
+      <c r="A10" s="2">
         <v>5</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="23"/>
+      <c r="C10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="18">
-        <v>0</v>
-      </c>
-      <c r="E10" s="18">
-        <v>0</v>
-      </c>
-      <c r="F10" s="18">
-        <v>0</v>
-      </c>
-      <c r="G10" s="18">
-        <v>0</v>
-      </c>
-      <c r="H10" s="18">
-        <v>0</v>
-      </c>
-      <c r="I10" s="18">
-        <v>0</v>
-      </c>
-      <c r="J10" s="18">
-        <v>0</v>
-      </c>
-      <c r="K10" s="18">
-        <v>0</v>
-      </c>
-      <c r="L10" s="18">
-        <v>0</v>
-      </c>
-      <c r="M10" s="18">
-        <v>0</v>
-      </c>
-      <c r="N10" s="18">
-        <v>0</v>
-      </c>
-      <c r="O10" s="18">
-        <v>0</v>
-      </c>
-      <c r="P10" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="18">
-        <v>0</v>
-      </c>
-      <c r="R10" s="18">
-        <v>0</v>
-      </c>
-      <c r="S10" s="18">
-        <v>0</v>
-      </c>
-      <c r="T10" s="18">
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11">
+        <v>0</v>
+      </c>
+      <c r="K10" s="11">
+        <v>0</v>
+      </c>
+      <c r="L10" s="11">
+        <v>0</v>
+      </c>
+      <c r="M10" s="11">
+        <v>0</v>
+      </c>
+      <c r="N10" s="11">
+        <v>0</v>
+      </c>
+      <c r="O10" s="11">
+        <v>0</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>0</v>
+      </c>
+      <c r="T10" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U10" s="18">
-        <v>0</v>
-      </c>
-      <c r="V10" s="18">
-        <v>0</v>
-      </c>
-      <c r="W10" s="18">
-        <v>0</v>
-      </c>
-      <c r="X10" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="19">
+      <c r="U10" s="11">
+        <v>0</v>
+      </c>
+      <c r="V10" s="11">
+        <v>0</v>
+      </c>
+      <c r="W10" s="11">
+        <v>0</v>
+      </c>
+      <c r="X10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A11" s="17">
+      <c r="A11" s="2">
         <v>6</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="17" t="s">
+      <c r="B11" s="23"/>
+      <c r="C11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="18">
-        <v>0</v>
-      </c>
-      <c r="E11" s="18">
-        <v>0</v>
-      </c>
-      <c r="F11" s="18">
-        <v>0</v>
-      </c>
-      <c r="G11" s="18">
-        <v>0</v>
-      </c>
-      <c r="H11" s="18">
-        <v>0</v>
-      </c>
-      <c r="I11" s="18">
-        <v>0</v>
-      </c>
-      <c r="J11" s="18">
-        <v>0</v>
-      </c>
-      <c r="K11" s="18">
-        <v>0</v>
-      </c>
-      <c r="L11" s="18">
-        <v>0</v>
-      </c>
-      <c r="M11" s="18">
-        <v>0</v>
-      </c>
-      <c r="N11" s="18">
-        <v>0</v>
-      </c>
-      <c r="O11" s="18">
-        <v>0</v>
-      </c>
-      <c r="P11" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="18">
-        <v>0</v>
-      </c>
-      <c r="R11" s="18">
-        <v>0</v>
-      </c>
-      <c r="S11" s="18">
-        <v>0</v>
-      </c>
-      <c r="T11" s="18">
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="11">
+        <v>0</v>
+      </c>
+      <c r="L11" s="11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11">
+        <v>0</v>
+      </c>
+      <c r="N11" s="11">
+        <v>0</v>
+      </c>
+      <c r="O11" s="11">
+        <v>0</v>
+      </c>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>0</v>
+      </c>
+      <c r="T11" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U11" s="18">
-        <v>0</v>
-      </c>
-      <c r="V11" s="18">
-        <v>0</v>
-      </c>
-      <c r="W11" s="18">
-        <v>0</v>
-      </c>
-      <c r="X11" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="19">
+      <c r="U11" s="11">
+        <v>0</v>
+      </c>
+      <c r="V11" s="11">
+        <v>0</v>
+      </c>
+      <c r="W11" s="11">
+        <v>0</v>
+      </c>
+      <c r="X11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A12" s="17">
+      <c r="A12" s="2">
         <v>7</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="17" t="s">
+      <c r="B12" s="23"/>
+      <c r="C12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="18">
-        <v>0</v>
-      </c>
-      <c r="E12" s="18">
-        <v>0</v>
-      </c>
-      <c r="F12" s="18">
-        <v>0</v>
-      </c>
-      <c r="G12" s="18">
-        <v>0</v>
-      </c>
-      <c r="H12" s="18">
-        <v>0</v>
-      </c>
-      <c r="I12" s="18">
-        <v>0</v>
-      </c>
-      <c r="J12" s="18">
-        <v>0</v>
-      </c>
-      <c r="K12" s="18">
-        <v>0</v>
-      </c>
-      <c r="L12" s="18">
-        <v>0</v>
-      </c>
-      <c r="M12" s="18">
-        <v>0</v>
-      </c>
-      <c r="N12" s="18">
-        <v>0</v>
-      </c>
-      <c r="O12" s="18">
-        <v>0</v>
-      </c>
-      <c r="P12" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="18">
-        <v>0</v>
-      </c>
-      <c r="R12" s="18">
-        <v>0</v>
-      </c>
-      <c r="S12" s="18">
-        <v>0</v>
-      </c>
-      <c r="T12" s="18">
+      <c r="D12" s="11">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <v>0</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0</v>
+      </c>
+      <c r="J12" s="11">
+        <v>0</v>
+      </c>
+      <c r="K12" s="11">
+        <v>0</v>
+      </c>
+      <c r="L12" s="11">
+        <v>0</v>
+      </c>
+      <c r="M12" s="11">
+        <v>0</v>
+      </c>
+      <c r="N12" s="11">
+        <v>0</v>
+      </c>
+      <c r="O12" s="11">
+        <v>0</v>
+      </c>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>0</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>0</v>
+      </c>
+      <c r="T12" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U12" s="18">
-        <v>0</v>
-      </c>
-      <c r="V12" s="18">
-        <v>0</v>
-      </c>
-      <c r="W12" s="18">
-        <v>0</v>
-      </c>
-      <c r="X12" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="19">
+      <c r="U12" s="11">
+        <v>0</v>
+      </c>
+      <c r="V12" s="11">
+        <v>0</v>
+      </c>
+      <c r="W12" s="11">
+        <v>0</v>
+      </c>
+      <c r="X12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A13" s="20">
+      <c r="A13" s="1">
         <v>8</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="24">
         <v>3</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="20">
-        <v>0</v>
-      </c>
-      <c r="E13" s="20">
-        <v>0</v>
-      </c>
-      <c r="F13" s="20">
-        <v>0</v>
-      </c>
-      <c r="G13" s="20">
-        <v>0</v>
-      </c>
-      <c r="H13" s="20">
-        <v>0</v>
-      </c>
-      <c r="I13" s="20">
-        <v>0</v>
-      </c>
-      <c r="J13" s="20">
-        <v>0</v>
-      </c>
-      <c r="K13" s="20">
-        <v>0</v>
-      </c>
-      <c r="L13" s="20">
-        <v>0</v>
-      </c>
-      <c r="M13" s="20">
-        <v>0</v>
-      </c>
-      <c r="N13" s="20">
-        <v>0</v>
-      </c>
-      <c r="O13" s="20">
-        <v>0</v>
-      </c>
-      <c r="P13" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="20">
-        <v>0</v>
-      </c>
-      <c r="R13" s="20">
-        <v>0</v>
-      </c>
-      <c r="S13" s="20">
-        <v>0</v>
-      </c>
-      <c r="T13" s="20">
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U13" s="20">
-        <v>0</v>
-      </c>
-      <c r="V13" s="20">
-        <v>0</v>
-      </c>
-      <c r="W13" s="20">
-        <v>0</v>
-      </c>
-      <c r="X13" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="29">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="29">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="29">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="29">
+      <c r="U13" s="1">
+        <v>0</v>
+      </c>
+      <c r="V13" s="1">
+        <v>0</v>
+      </c>
+      <c r="W13" s="1">
+        <v>0</v>
+      </c>
+      <c r="X13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A14" s="20">
+      <c r="A14" s="1">
         <v>9</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="20" t="s">
+      <c r="B14" s="24"/>
+      <c r="C14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="20">
-        <v>0</v>
-      </c>
-      <c r="E14" s="20">
-        <v>0</v>
-      </c>
-      <c r="F14" s="20">
-        <v>0</v>
-      </c>
-      <c r="G14" s="20">
-        <v>0</v>
-      </c>
-      <c r="H14" s="20">
-        <v>0</v>
-      </c>
-      <c r="I14" s="20">
-        <v>0</v>
-      </c>
-      <c r="J14" s="20">
-        <v>0</v>
-      </c>
-      <c r="K14" s="20">
-        <v>0</v>
-      </c>
-      <c r="L14" s="20">
-        <v>0</v>
-      </c>
-      <c r="M14" s="20">
-        <v>0</v>
-      </c>
-      <c r="N14" s="20">
-        <v>0</v>
-      </c>
-      <c r="O14" s="20">
-        <v>0</v>
-      </c>
-      <c r="P14" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="20">
-        <v>0</v>
-      </c>
-      <c r="R14" s="20">
-        <v>0</v>
-      </c>
-      <c r="S14" s="20">
-        <v>0</v>
-      </c>
-      <c r="T14" s="20">
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U14" s="20">
-        <v>0</v>
-      </c>
-      <c r="V14" s="20">
-        <v>0</v>
-      </c>
-      <c r="W14" s="20">
-        <v>0</v>
-      </c>
-      <c r="X14" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="29">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="29">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="29">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="29">
+      <c r="U14" s="1">
+        <v>0</v>
+      </c>
+      <c r="V14" s="1">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A15" s="20">
+      <c r="A15" s="1">
         <v>10</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="20" t="s">
+      <c r="B15" s="24"/>
+      <c r="C15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="20">
-        <v>0</v>
-      </c>
-      <c r="E15" s="20">
-        <v>0</v>
-      </c>
-      <c r="F15" s="20">
-        <v>0</v>
-      </c>
-      <c r="G15" s="20">
-        <v>0</v>
-      </c>
-      <c r="H15" s="20">
-        <v>0</v>
-      </c>
-      <c r="I15" s="20">
-        <v>0</v>
-      </c>
-      <c r="J15" s="20">
-        <v>0</v>
-      </c>
-      <c r="K15" s="20">
-        <v>0</v>
-      </c>
-      <c r="L15" s="20">
-        <v>0</v>
-      </c>
-      <c r="M15" s="20">
-        <v>0</v>
-      </c>
-      <c r="N15" s="20">
-        <v>0</v>
-      </c>
-      <c r="O15" s="20">
-        <v>0</v>
-      </c>
-      <c r="P15" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="20">
-        <v>0</v>
-      </c>
-      <c r="R15" s="20">
-        <v>0</v>
-      </c>
-      <c r="S15" s="20">
-        <v>0</v>
-      </c>
-      <c r="T15" s="20">
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U15" s="20">
-        <v>0</v>
-      </c>
-      <c r="V15" s="20">
-        <v>0</v>
-      </c>
-      <c r="W15" s="20">
-        <v>0</v>
-      </c>
-      <c r="X15" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="29">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="29">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="29">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="29">
+      <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A16" s="20">
+      <c r="A16" s="1">
         <v>11</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="20" t="s">
+      <c r="B16" s="24"/>
+      <c r="C16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="20">
-        <v>0</v>
-      </c>
-      <c r="E16" s="20">
-        <v>0</v>
-      </c>
-      <c r="F16" s="20">
-        <v>0</v>
-      </c>
-      <c r="G16" s="20">
-        <v>0</v>
-      </c>
-      <c r="H16" s="20">
-        <v>0</v>
-      </c>
-      <c r="I16" s="20">
-        <v>0</v>
-      </c>
-      <c r="J16" s="20">
-        <v>0</v>
-      </c>
-      <c r="K16" s="20">
-        <v>0</v>
-      </c>
-      <c r="L16" s="20">
-        <v>0</v>
-      </c>
-      <c r="M16" s="20">
-        <v>0</v>
-      </c>
-      <c r="N16" s="20">
-        <v>0</v>
-      </c>
-      <c r="O16" s="20">
-        <v>0</v>
-      </c>
-      <c r="P16" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="20">
-        <v>0</v>
-      </c>
-      <c r="R16" s="20">
-        <v>0</v>
-      </c>
-      <c r="S16" s="20">
-        <v>0</v>
-      </c>
-      <c r="T16" s="20">
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U16" s="20">
-        <v>0</v>
-      </c>
-      <c r="V16" s="20">
-        <v>0</v>
-      </c>
-      <c r="W16" s="20">
-        <v>0</v>
-      </c>
-      <c r="X16" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="29">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="29">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="29">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="29">
+      <c r="U16" s="1">
+        <v>0</v>
+      </c>
+      <c r="V16" s="1">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1">
+        <v>0</v>
+      </c>
+      <c r="X16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:113" x14ac:dyDescent="0.2">
-      <c r="A17" s="20">
+      <c r="A17" s="1">
         <v>12</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="20" t="s">
+      <c r="B17" s="24"/>
+      <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="20">
-        <v>0</v>
-      </c>
-      <c r="E17" s="20">
-        <v>0</v>
-      </c>
-      <c r="F17" s="20">
-        <v>0</v>
-      </c>
-      <c r="G17" s="20">
-        <v>0</v>
-      </c>
-      <c r="H17" s="20">
-        <v>0</v>
-      </c>
-      <c r="I17" s="20">
-        <v>0</v>
-      </c>
-      <c r="J17" s="20">
-        <v>0</v>
-      </c>
-      <c r="K17" s="20">
-        <v>0</v>
-      </c>
-      <c r="L17" s="20">
-        <v>0</v>
-      </c>
-      <c r="M17" s="20">
-        <v>0</v>
-      </c>
-      <c r="N17" s="20">
-        <v>0</v>
-      </c>
-      <c r="O17" s="20">
-        <v>0</v>
-      </c>
-      <c r="P17" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="20">
-        <v>0</v>
-      </c>
-      <c r="R17" s="20">
-        <v>0</v>
-      </c>
-      <c r="S17" s="20">
-        <v>0</v>
-      </c>
-      <c r="T17" s="20">
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U17" s="20">
-        <v>0</v>
-      </c>
-      <c r="V17" s="20">
-        <v>0</v>
-      </c>
-      <c r="W17" s="20">
-        <v>0</v>
-      </c>
-      <c r="X17" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="29">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="29">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="29">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="29">
+      <c r="U17" s="1">
+        <v>0</v>
+      </c>
+      <c r="V17" s="1">
+        <v>0</v>
+      </c>
+      <c r="W17" s="1">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:113" x14ac:dyDescent="0.2">
-      <c r="A18" s="20">
+      <c r="A18" s="1">
         <v>13</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="20" t="s">
+      <c r="B18" s="24"/>
+      <c r="C18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="20">
-        <v>0</v>
-      </c>
-      <c r="E18" s="20">
-        <v>0</v>
-      </c>
-      <c r="F18" s="20">
-        <v>0</v>
-      </c>
-      <c r="G18" s="20">
-        <v>0</v>
-      </c>
-      <c r="H18" s="20">
-        <v>0</v>
-      </c>
-      <c r="I18" s="20">
-        <v>0</v>
-      </c>
-      <c r="J18" s="20">
-        <v>0</v>
-      </c>
-      <c r="K18" s="20">
-        <v>0</v>
-      </c>
-      <c r="L18" s="20">
-        <v>0</v>
-      </c>
-      <c r="M18" s="20">
-        <v>0</v>
-      </c>
-      <c r="N18" s="20">
-        <v>0</v>
-      </c>
-      <c r="O18" s="20">
-        <v>0</v>
-      </c>
-      <c r="P18" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="20">
-        <v>0</v>
-      </c>
-      <c r="R18" s="20">
-        <v>0</v>
-      </c>
-      <c r="S18" s="20">
-        <v>0</v>
-      </c>
-      <c r="T18" s="20">
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U18" s="20">
-        <v>0</v>
-      </c>
-      <c r="V18" s="20">
-        <v>0</v>
-      </c>
-      <c r="W18" s="20">
-        <v>0</v>
-      </c>
-      <c r="X18" s="20">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="29">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="29">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="29">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="29">
+      <c r="U18" s="1">
+        <v>0</v>
+      </c>
+      <c r="V18" s="1">
+        <v>0</v>
+      </c>
+      <c r="W18" s="1">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21" t="s">
+      <c r="B19" s="13"/>
+      <c r="C19" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="14">
         <f t="shared" ref="D19:AG19" si="1">SUM(D5:D16)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="22">
+      <c r="J19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K19" s="22">
+      <c r="K19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L19" s="22">
+      <c r="L19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M19" s="22">
+      <c r="M19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N19" s="22">
+      <c r="N19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O19" s="22">
+      <c r="O19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P19" s="22">
+      <c r="P19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="22">
+      <c r="Q19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R19" s="22">
+      <c r="R19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S19" s="22">
+      <c r="S19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T19" s="22">
+      <c r="T19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U19" s="22">
+      <c r="U19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V19" s="22">
+      <c r="V19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W19" s="22">
+      <c r="W19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X19" s="22">
+      <c r="X19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y19" s="22">
+      <c r="Y19" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z19" s="23">
+      <c r="Z19" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="23">
+      <c r="AA19" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB19" s="23">
+      <c r="AB19" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC19" s="23">
+      <c r="AC19" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD19" s="23">
+      <c r="AD19" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE19" s="23">
+      <c r="AE19" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF19" s="23">
+      <c r="AF19" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG19" s="23">
+      <c r="AG19" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21" t="s">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="14">
         <f t="shared" ref="D20:AG20" si="2">SUM(D6:D19)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="22">
+      <c r="J20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K20" s="22">
+      <c r="K20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="22">
+      <c r="L20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M20" s="22">
+      <c r="M20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N20" s="22">
+      <c r="N20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O20" s="22">
+      <c r="O20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P20" s="22">
+      <c r="P20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="22">
+      <c r="Q20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R20" s="22">
+      <c r="R20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S20" s="22">
+      <c r="S20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T20" s="22">
+      <c r="T20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U20" s="22">
+      <c r="U20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V20" s="22">
+      <c r="V20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W20" s="22">
+      <c r="W20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X20" s="22">
+      <c r="X20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y20" s="22">
+      <c r="Y20" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z20" s="24">
+      <c r="Z20" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="24">
+      <c r="AA20" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AB20" s="24">
+      <c r="AB20" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC20" s="24">
+      <c r="AC20" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD20" s="24">
+      <c r="AD20" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AE20" s="24">
+      <c r="AE20" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AF20" s="24">
+      <c r="AF20" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="24">
+      <c r="AG20" s="28">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:113" x14ac:dyDescent="0.2">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="26" t="s">
+      <c r="B21" s="16"/>
+      <c r="C21" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="14">
         <f t="shared" ref="D21:AD21" si="3">D19-D20</f>
         <v>0</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="22">
+      <c r="J21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K21" s="22">
+      <c r="K21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L21" s="22">
+      <c r="L21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M21" s="22">
+      <c r="M21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N21" s="22">
+      <c r="N21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O21" s="22">
+      <c r="O21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P21" s="22">
+      <c r="P21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="22">
+      <c r="Q21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R21" s="22">
+      <c r="R21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S21" s="22">
+      <c r="S21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T21" s="22">
+      <c r="T21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U21" s="22">
+      <c r="U21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V21" s="22">
+      <c r="V21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W21" s="22">
+      <c r="W21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X21" s="27">
+      <c r="X21" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y21" s="22">
+      <c r="Y21" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z21" s="23">
+      <c r="Z21" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA21" s="23">
+      <c r="AA21" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB21" s="23">
+      <c r="AB21" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC21" s="23">
+      <c r="AC21" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AD21" s="23">
+      <c r="AD21" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE21" s="28"/>
-      <c r="AF21" s="23"/>
-      <c r="AG21" s="23"/>
+      <c r="AE21" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="15">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:113" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="Z22" s="9"/>
-      <c r="AA22" s="9"/>
-      <c r="AB22" s="9"/>
-      <c r="AC22" s="9"/>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="9"/>
-      <c r="AG22" s="9"/>
+    <row r="22" spans="1:113" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="Z22" s="5"/>
+      <c r="AA22" s="5"/>
+      <c r="AB22" s="5"/>
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="5"/>
+      <c r="AE22" s="5"/>
+      <c r="AF22" s="5"/>
+      <c r="AG22" s="5"/>
       <c r="AH22"/>
       <c r="AI22"/>
       <c r="AJ22"/>
@@ -2821,16 +2824,16 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:K2"/>
+    <mergeCell ref="L2:S2"/>
+    <mergeCell ref="T2:T4"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="Y2:Y4"/>
     <mergeCell ref="Z2:AA2"/>
     <mergeCell ref="AB2:AC2"/>
     <mergeCell ref="AD2:AD4"/>
@@ -2847,16 +2850,16 @@
     <mergeCell ref="V3:V4"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:K2"/>
-    <mergeCell ref="L2:S2"/>
-    <mergeCell ref="T2:T4"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="Y2:Y4"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AE3:AE4"/>
   </mergeCells>
   <conditionalFormatting sqref="AD8:AG8">
     <cfRule type="dataBar" priority="3">

--- a/docs/template/summary.xlsx
+++ b/docs/template/summary.xlsx
@@ -3,12 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/restupriyono/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73FA6D2-4BBD-0842-979B-FDC89C355B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6274C4-3184-4548-9263-415D42EEF212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -189,7 +184,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(&quot;IDR&quot;* #,##0_);_(&quot;IDR&quot;* \(#,##0\);_(&quot;IDR&quot;* \-_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -211,6 +206,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -341,9 +341,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -354,7 +354,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -366,20 +378,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -388,6 +412,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -399,34 +426,10 @@
     <xf numFmtId="1" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -690,2057 +693,2051 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DI22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="6.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="4.6640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" style="5" customWidth="1"/>
-    <col min="5" max="11" width="5.83203125" style="5" customWidth="1"/>
-    <col min="12" max="19" width="6.5" style="5"/>
-    <col min="20" max="23" width="5.6640625" style="5" customWidth="1"/>
-    <col min="24" max="24" width="8.6640625" style="5" customWidth="1"/>
-    <col min="25" max="25" width="5.6640625" style="5" customWidth="1"/>
-    <col min="26" max="26" width="13" style="5" customWidth="1"/>
-    <col min="27" max="27" width="11.6640625" style="5" customWidth="1"/>
-    <col min="28" max="28" width="13" style="5" customWidth="1"/>
-    <col min="29" max="31" width="11.6640625" style="5" customWidth="1"/>
-    <col min="32" max="32" width="12.1640625" style="5" customWidth="1"/>
-    <col min="33" max="33" width="11.6640625" style="5" customWidth="1"/>
-    <col min="114" max="16304" width="6.5" style="5"/>
-    <col min="16305" max="16384" width="10.5" style="5" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="4.6640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" style="9" customWidth="1"/>
+    <col min="5" max="11" width="5.83203125" style="9" customWidth="1"/>
+    <col min="12" max="19" width="6.5" style="9"/>
+    <col min="20" max="23" width="5.6640625" style="9" customWidth="1"/>
+    <col min="24" max="24" width="8.6640625" style="9" customWidth="1"/>
+    <col min="25" max="25" width="5.6640625" style="9" customWidth="1"/>
+    <col min="26" max="26" width="13" style="9" customWidth="1"/>
+    <col min="27" max="27" width="11.6640625" style="9" customWidth="1"/>
+    <col min="28" max="28" width="13" style="9" customWidth="1"/>
+    <col min="29" max="31" width="11.6640625" style="9" customWidth="1"/>
+    <col min="32" max="32" width="12.1640625" style="9" customWidth="1"/>
+    <col min="33" max="33" width="11.6640625" style="9" customWidth="1"/>
+    <col min="114" max="16304" width="6.5" style="9"/>
+    <col min="16305" max="16384" width="10.5" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="7"/>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="7"/>
-      <c r="AG1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
     </row>
     <row r="2" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26" t="s">
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26" t="s">
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="26" t="s">
+      <c r="U2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="4" t="s">
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="Y2" s="26" t="s">
+      <c r="Y2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="Z2" s="26" t="s">
+      <c r="Z2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="26" t="s">
+      <c r="AA2" s="7"/>
+      <c r="AB2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="25" t="s">
+      <c r="AC2" s="7"/>
+      <c r="AD2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AE2" s="21" t="s">
+      <c r="AE2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="21"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
     </row>
     <row r="3" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26" t="s">
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="M3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="N3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="O3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26" t="s">
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="V3" s="26" t="s">
+      <c r="V3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="W3" s="26" t="s">
+      <c r="W3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="X3" s="26" t="s">
+      <c r="X3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="25" t="s">
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AA3" s="26" t="s">
+      <c r="AA3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AB3" s="25" t="s">
+      <c r="AB3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AC3" s="26" t="s">
+      <c r="AC3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="20" t="s">
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AF3" s="20" t="s">
+      <c r="AF3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AG3" s="21" t="s">
+      <c r="AG3" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="4" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="4" t="s">
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26"/>
-      <c r="V4" s="26"/>
-      <c r="W4" s="26"/>
-      <c r="X4" s="26"/>
-      <c r="Y4" s="26"/>
-      <c r="Z4" s="25"/>
-      <c r="AA4" s="26"/>
-      <c r="AB4" s="25"/>
-      <c r="AC4" s="26"/>
-      <c r="AD4" s="25"/>
-      <c r="AE4" s="20"/>
-      <c r="AF4" s="20"/>
-      <c r="AG4" s="21"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="7"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="4"/>
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="5"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="13">
         <v>1</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="8">
-        <v>0</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0</v>
-      </c>
-      <c r="F5" s="8">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8">
-        <v>0</v>
-      </c>
-      <c r="O5" s="8">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0</v>
-      </c>
-      <c r="S5" s="8">
-        <v>0</v>
-      </c>
-      <c r="T5" s="8">
+      <c r="D5" s="14">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14">
+        <v>0</v>
+      </c>
+      <c r="L5" s="14">
+        <v>0</v>
+      </c>
+      <c r="M5" s="14">
+        <v>0</v>
+      </c>
+      <c r="N5" s="14">
+        <v>0</v>
+      </c>
+      <c r="O5" s="14">
+        <v>0</v>
+      </c>
+      <c r="P5" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>0</v>
+      </c>
+      <c r="R5" s="14">
+        <v>0</v>
+      </c>
+      <c r="S5" s="14">
+        <v>0</v>
+      </c>
+      <c r="T5" s="14">
         <f t="shared" ref="T5:T18" si="0">G5+N5</f>
         <v>0</v>
       </c>
-      <c r="U5" s="8">
-        <v>0</v>
-      </c>
-      <c r="V5" s="8">
-        <v>0</v>
-      </c>
-      <c r="W5" s="8">
-        <v>0</v>
-      </c>
-      <c r="X5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="10">
+      <c r="U5" s="14">
+        <v>0</v>
+      </c>
+      <c r="V5" s="14">
+        <v>0</v>
+      </c>
+      <c r="W5" s="14">
+        <v>0</v>
+      </c>
+      <c r="X5" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="15">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="15">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="16">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="A6" s="13">
         <v>2</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="8">
-        <v>0</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0</v>
-      </c>
-      <c r="F6" s="8">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0</v>
-      </c>
-      <c r="I6" s="8">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8">
-        <v>0</v>
-      </c>
-      <c r="K6" s="8">
-        <v>0</v>
-      </c>
-      <c r="L6" s="8">
-        <v>0</v>
-      </c>
-      <c r="M6" s="8">
-        <v>0</v>
-      </c>
-      <c r="N6" s="8">
-        <v>0</v>
-      </c>
-      <c r="O6" s="8">
-        <v>0</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
-        <v>0</v>
-      </c>
-      <c r="S6" s="8">
-        <v>0</v>
-      </c>
-      <c r="T6" s="8">
+      <c r="D6" s="14">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14">
+        <v>0</v>
+      </c>
+      <c r="J6" s="14">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14">
+        <v>0</v>
+      </c>
+      <c r="L6" s="14">
+        <v>0</v>
+      </c>
+      <c r="M6" s="14">
+        <v>0</v>
+      </c>
+      <c r="N6" s="14">
+        <v>0</v>
+      </c>
+      <c r="O6" s="14">
+        <v>0</v>
+      </c>
+      <c r="P6" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>0</v>
+      </c>
+      <c r="R6" s="14">
+        <v>0</v>
+      </c>
+      <c r="S6" s="14">
+        <v>0</v>
+      </c>
+      <c r="T6" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U6" s="8">
-        <v>0</v>
-      </c>
-      <c r="V6" s="8">
-        <v>0</v>
-      </c>
-      <c r="W6" s="8">
-        <v>0</v>
-      </c>
-      <c r="X6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="10">
+      <c r="U6" s="14">
+        <v>0</v>
+      </c>
+      <c r="V6" s="14">
+        <v>0</v>
+      </c>
+      <c r="W6" s="14">
+        <v>0</v>
+      </c>
+      <c r="X6" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="15">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="15">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="16">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+      <c r="A7" s="13">
         <v>3</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="8">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8">
-        <v>0</v>
-      </c>
-      <c r="O7" s="8">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <v>0</v>
-      </c>
-      <c r="S7" s="8">
-        <v>0</v>
-      </c>
-      <c r="T7" s="8">
+      <c r="D7" s="14">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14">
+        <v>0</v>
+      </c>
+      <c r="L7" s="14">
+        <v>0</v>
+      </c>
+      <c r="M7" s="14">
+        <v>0</v>
+      </c>
+      <c r="N7" s="14">
+        <v>0</v>
+      </c>
+      <c r="O7" s="14">
+        <v>0</v>
+      </c>
+      <c r="P7" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>0</v>
+      </c>
+      <c r="R7" s="14">
+        <v>0</v>
+      </c>
+      <c r="S7" s="14">
+        <v>0</v>
+      </c>
+      <c r="T7" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U7" s="8">
-        <v>0</v>
-      </c>
-      <c r="V7" s="8">
-        <v>0</v>
-      </c>
-      <c r="W7" s="8">
-        <v>0</v>
-      </c>
-      <c r="X7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="9">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="10">
+      <c r="U7" s="14">
+        <v>0</v>
+      </c>
+      <c r="V7" s="14">
+        <v>0</v>
+      </c>
+      <c r="W7" s="14">
+        <v>0</v>
+      </c>
+      <c r="X7" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="16">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+      <c r="A8" s="17">
         <v>3</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="2">
         <v>2</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="11">
-        <v>0</v>
-      </c>
-      <c r="E8" s="11">
-        <v>0</v>
-      </c>
-      <c r="F8" s="11">
-        <v>0</v>
-      </c>
-      <c r="G8" s="11">
-        <v>0</v>
-      </c>
-      <c r="H8" s="11">
-        <v>0</v>
-      </c>
-      <c r="I8" s="11">
-        <v>0</v>
-      </c>
-      <c r="J8" s="11">
-        <v>0</v>
-      </c>
-      <c r="K8" s="11">
-        <v>0</v>
-      </c>
-      <c r="L8" s="11">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11">
-        <v>0</v>
-      </c>
-      <c r="N8" s="11">
-        <v>0</v>
-      </c>
-      <c r="O8" s="11">
-        <v>0</v>
-      </c>
-      <c r="P8" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>0</v>
-      </c>
-      <c r="R8" s="11">
-        <v>0</v>
-      </c>
-      <c r="S8" s="11">
-        <v>0</v>
-      </c>
-      <c r="T8" s="11">
+      <c r="D8" s="18">
+        <v>0</v>
+      </c>
+      <c r="E8" s="18">
+        <v>0</v>
+      </c>
+      <c r="F8" s="18">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18">
+        <v>0</v>
+      </c>
+      <c r="H8" s="18">
+        <v>0</v>
+      </c>
+      <c r="I8" s="18">
+        <v>0</v>
+      </c>
+      <c r="J8" s="18">
+        <v>0</v>
+      </c>
+      <c r="K8" s="18">
+        <v>0</v>
+      </c>
+      <c r="L8" s="18">
+        <v>0</v>
+      </c>
+      <c r="M8" s="18">
+        <v>0</v>
+      </c>
+      <c r="N8" s="18">
+        <v>0</v>
+      </c>
+      <c r="O8" s="18">
+        <v>0</v>
+      </c>
+      <c r="P8" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="18">
+        <v>0</v>
+      </c>
+      <c r="R8" s="18">
+        <v>0</v>
+      </c>
+      <c r="S8" s="18">
+        <v>0</v>
+      </c>
+      <c r="T8" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U8" s="11">
-        <v>0</v>
-      </c>
-      <c r="V8" s="11">
-        <v>0</v>
-      </c>
-      <c r="W8" s="11">
-        <v>0</v>
-      </c>
-      <c r="X8" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="12">
+      <c r="U8" s="18">
+        <v>0</v>
+      </c>
+      <c r="V8" s="18">
+        <v>0</v>
+      </c>
+      <c r="W8" s="18">
+        <v>0</v>
+      </c>
+      <c r="X8" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
+      <c r="A9" s="17">
         <v>4</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="11">
-        <v>0</v>
-      </c>
-      <c r="E9" s="11">
-        <v>0</v>
-      </c>
-      <c r="F9" s="11">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
-        <v>0</v>
-      </c>
-      <c r="H9" s="11">
-        <v>0</v>
-      </c>
-      <c r="I9" s="11">
-        <v>0</v>
-      </c>
-      <c r="J9" s="11">
-        <v>0</v>
-      </c>
-      <c r="K9" s="11">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11">
-        <v>0</v>
-      </c>
-      <c r="M9" s="11">
-        <v>0</v>
-      </c>
-      <c r="N9" s="11">
-        <v>0</v>
-      </c>
-      <c r="O9" s="11">
-        <v>0</v>
-      </c>
-      <c r="P9" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>0</v>
-      </c>
-      <c r="R9" s="11">
-        <v>0</v>
-      </c>
-      <c r="S9" s="11">
-        <v>0</v>
-      </c>
-      <c r="T9" s="11">
+      <c r="D9" s="18">
+        <v>0</v>
+      </c>
+      <c r="E9" s="18">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18">
+        <v>0</v>
+      </c>
+      <c r="H9" s="18">
+        <v>0</v>
+      </c>
+      <c r="I9" s="18">
+        <v>0</v>
+      </c>
+      <c r="J9" s="18">
+        <v>0</v>
+      </c>
+      <c r="K9" s="18">
+        <v>0</v>
+      </c>
+      <c r="L9" s="18">
+        <v>0</v>
+      </c>
+      <c r="M9" s="18">
+        <v>0</v>
+      </c>
+      <c r="N9" s="18">
+        <v>0</v>
+      </c>
+      <c r="O9" s="18">
+        <v>0</v>
+      </c>
+      <c r="P9" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="18">
+        <v>0</v>
+      </c>
+      <c r="R9" s="18">
+        <v>0</v>
+      </c>
+      <c r="S9" s="18">
+        <v>0</v>
+      </c>
+      <c r="T9" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U9" s="11">
-        <v>0</v>
-      </c>
-      <c r="V9" s="11">
-        <v>0</v>
-      </c>
-      <c r="W9" s="11">
-        <v>0</v>
-      </c>
-      <c r="X9" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="12">
+      <c r="U9" s="18">
+        <v>0</v>
+      </c>
+      <c r="V9" s="18">
+        <v>0</v>
+      </c>
+      <c r="W9" s="18">
+        <v>0</v>
+      </c>
+      <c r="X9" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
+      <c r="A10" s="17">
         <v>5</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="2"/>
+      <c r="C10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="11">
-        <v>0</v>
-      </c>
-      <c r="E10" s="11">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <v>0</v>
-      </c>
-      <c r="H10" s="11">
-        <v>0</v>
-      </c>
-      <c r="I10" s="11">
-        <v>0</v>
-      </c>
-      <c r="J10" s="11">
-        <v>0</v>
-      </c>
-      <c r="K10" s="11">
-        <v>0</v>
-      </c>
-      <c r="L10" s="11">
-        <v>0</v>
-      </c>
-      <c r="M10" s="11">
-        <v>0</v>
-      </c>
-      <c r="N10" s="11">
-        <v>0</v>
-      </c>
-      <c r="O10" s="11">
-        <v>0</v>
-      </c>
-      <c r="P10" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>0</v>
-      </c>
-      <c r="R10" s="11">
-        <v>0</v>
-      </c>
-      <c r="S10" s="11">
-        <v>0</v>
-      </c>
-      <c r="T10" s="11">
+      <c r="D10" s="18">
+        <v>0</v>
+      </c>
+      <c r="E10" s="18">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18">
+        <v>0</v>
+      </c>
+      <c r="I10" s="18">
+        <v>0</v>
+      </c>
+      <c r="J10" s="18">
+        <v>0</v>
+      </c>
+      <c r="K10" s="18">
+        <v>0</v>
+      </c>
+      <c r="L10" s="18">
+        <v>0</v>
+      </c>
+      <c r="M10" s="18">
+        <v>0</v>
+      </c>
+      <c r="N10" s="18">
+        <v>0</v>
+      </c>
+      <c r="O10" s="18">
+        <v>0</v>
+      </c>
+      <c r="P10" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="18">
+        <v>0</v>
+      </c>
+      <c r="R10" s="18">
+        <v>0</v>
+      </c>
+      <c r="S10" s="18">
+        <v>0</v>
+      </c>
+      <c r="T10" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U10" s="11">
-        <v>0</v>
-      </c>
-      <c r="V10" s="11">
-        <v>0</v>
-      </c>
-      <c r="W10" s="11">
-        <v>0</v>
-      </c>
-      <c r="X10" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="12">
+      <c r="U10" s="18">
+        <v>0</v>
+      </c>
+      <c r="V10" s="18">
+        <v>0</v>
+      </c>
+      <c r="W10" s="18">
+        <v>0</v>
+      </c>
+      <c r="X10" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
+      <c r="A11" s="17">
         <v>6</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="2" t="s">
+      <c r="B11" s="2"/>
+      <c r="C11" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="11">
-        <v>0</v>
-      </c>
-      <c r="E11" s="11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="11">
-        <v>0</v>
-      </c>
-      <c r="G11" s="11">
-        <v>0</v>
-      </c>
-      <c r="H11" s="11">
-        <v>0</v>
-      </c>
-      <c r="I11" s="11">
-        <v>0</v>
-      </c>
-      <c r="J11" s="11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="11">
-        <v>0</v>
-      </c>
-      <c r="L11" s="11">
-        <v>0</v>
-      </c>
-      <c r="M11" s="11">
-        <v>0</v>
-      </c>
-      <c r="N11" s="11">
-        <v>0</v>
-      </c>
-      <c r="O11" s="11">
-        <v>0</v>
-      </c>
-      <c r="P11" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>0</v>
-      </c>
-      <c r="R11" s="11">
-        <v>0</v>
-      </c>
-      <c r="S11" s="11">
-        <v>0</v>
-      </c>
-      <c r="T11" s="11">
+      <c r="D11" s="18">
+        <v>0</v>
+      </c>
+      <c r="E11" s="18">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18">
+        <v>0</v>
+      </c>
+      <c r="I11" s="18">
+        <v>0</v>
+      </c>
+      <c r="J11" s="18">
+        <v>0</v>
+      </c>
+      <c r="K11" s="18">
+        <v>0</v>
+      </c>
+      <c r="L11" s="18">
+        <v>0</v>
+      </c>
+      <c r="M11" s="18">
+        <v>0</v>
+      </c>
+      <c r="N11" s="18">
+        <v>0</v>
+      </c>
+      <c r="O11" s="18">
+        <v>0</v>
+      </c>
+      <c r="P11" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="18">
+        <v>0</v>
+      </c>
+      <c r="R11" s="18">
+        <v>0</v>
+      </c>
+      <c r="S11" s="18">
+        <v>0</v>
+      </c>
+      <c r="T11" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U11" s="11">
-        <v>0</v>
-      </c>
-      <c r="V11" s="11">
-        <v>0</v>
-      </c>
-      <c r="W11" s="11">
-        <v>0</v>
-      </c>
-      <c r="X11" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="12">
+      <c r="U11" s="18">
+        <v>0</v>
+      </c>
+      <c r="V11" s="18">
+        <v>0</v>
+      </c>
+      <c r="W11" s="18">
+        <v>0</v>
+      </c>
+      <c r="X11" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
+      <c r="A12" s="17">
         <v>7</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="11">
-        <v>0</v>
-      </c>
-      <c r="E12" s="11">
-        <v>0</v>
-      </c>
-      <c r="F12" s="11">
-        <v>0</v>
-      </c>
-      <c r="G12" s="11">
-        <v>0</v>
-      </c>
-      <c r="H12" s="11">
-        <v>0</v>
-      </c>
-      <c r="I12" s="11">
-        <v>0</v>
-      </c>
-      <c r="J12" s="11">
-        <v>0</v>
-      </c>
-      <c r="K12" s="11">
-        <v>0</v>
-      </c>
-      <c r="L12" s="11">
-        <v>0</v>
-      </c>
-      <c r="M12" s="11">
-        <v>0</v>
-      </c>
-      <c r="N12" s="11">
-        <v>0</v>
-      </c>
-      <c r="O12" s="11">
-        <v>0</v>
-      </c>
-      <c r="P12" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>0</v>
-      </c>
-      <c r="R12" s="11">
-        <v>0</v>
-      </c>
-      <c r="S12" s="11">
-        <v>0</v>
-      </c>
-      <c r="T12" s="11">
+      <c r="D12" s="18">
+        <v>0</v>
+      </c>
+      <c r="E12" s="18">
+        <v>0</v>
+      </c>
+      <c r="F12" s="18">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18">
+        <v>0</v>
+      </c>
+      <c r="H12" s="18">
+        <v>0</v>
+      </c>
+      <c r="I12" s="18">
+        <v>0</v>
+      </c>
+      <c r="J12" s="18">
+        <v>0</v>
+      </c>
+      <c r="K12" s="18">
+        <v>0</v>
+      </c>
+      <c r="L12" s="18">
+        <v>0</v>
+      </c>
+      <c r="M12" s="18">
+        <v>0</v>
+      </c>
+      <c r="N12" s="18">
+        <v>0</v>
+      </c>
+      <c r="O12" s="18">
+        <v>0</v>
+      </c>
+      <c r="P12" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="18">
+        <v>0</v>
+      </c>
+      <c r="R12" s="18">
+        <v>0</v>
+      </c>
+      <c r="S12" s="18">
+        <v>0</v>
+      </c>
+      <c r="T12" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U12" s="11">
-        <v>0</v>
-      </c>
-      <c r="V12" s="11">
-        <v>0</v>
-      </c>
-      <c r="W12" s="11">
-        <v>0</v>
-      </c>
-      <c r="X12" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="12">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="12">
+      <c r="U12" s="18">
+        <v>0</v>
+      </c>
+      <c r="V12" s="18">
+        <v>0</v>
+      </c>
+      <c r="W12" s="18">
+        <v>0</v>
+      </c>
+      <c r="X12" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+      <c r="A13" s="20">
         <v>8</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="1">
         <v>3</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1">
-        <v>0</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-      <c r="P13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1">
-        <v>0</v>
-      </c>
-      <c r="T13" s="1">
+      <c r="D13" s="20">
+        <v>0</v>
+      </c>
+      <c r="E13" s="20">
+        <v>0</v>
+      </c>
+      <c r="F13" s="20">
+        <v>0</v>
+      </c>
+      <c r="G13" s="20">
+        <v>0</v>
+      </c>
+      <c r="H13" s="20">
+        <v>0</v>
+      </c>
+      <c r="I13" s="20">
+        <v>0</v>
+      </c>
+      <c r="J13" s="20">
+        <v>0</v>
+      </c>
+      <c r="K13" s="20">
+        <v>0</v>
+      </c>
+      <c r="L13" s="20">
+        <v>0</v>
+      </c>
+      <c r="M13" s="20">
+        <v>0</v>
+      </c>
+      <c r="N13" s="20">
+        <v>0</v>
+      </c>
+      <c r="O13" s="20">
+        <v>0</v>
+      </c>
+      <c r="P13" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="20">
+        <v>0</v>
+      </c>
+      <c r="R13" s="20">
+        <v>0</v>
+      </c>
+      <c r="S13" s="20">
+        <v>0</v>
+      </c>
+      <c r="T13" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U13" s="1">
-        <v>0</v>
-      </c>
-      <c r="V13" s="1">
-        <v>0</v>
-      </c>
-      <c r="W13" s="1">
-        <v>0</v>
-      </c>
-      <c r="X13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="19">
+      <c r="U13" s="20">
+        <v>0</v>
+      </c>
+      <c r="V13" s="20">
+        <v>0</v>
+      </c>
+      <c r="W13" s="20">
+        <v>0</v>
+      </c>
+      <c r="X13" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="29">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="29">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="29">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="29">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="29">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
+      <c r="A14" s="20">
         <v>9</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="1" t="s">
+      <c r="B14" s="1"/>
+      <c r="C14" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="S14" s="1">
-        <v>0</v>
-      </c>
-      <c r="T14" s="1">
+      <c r="D14" s="20">
+        <v>0</v>
+      </c>
+      <c r="E14" s="20">
+        <v>0</v>
+      </c>
+      <c r="F14" s="20">
+        <v>0</v>
+      </c>
+      <c r="G14" s="20">
+        <v>0</v>
+      </c>
+      <c r="H14" s="20">
+        <v>0</v>
+      </c>
+      <c r="I14" s="20">
+        <v>0</v>
+      </c>
+      <c r="J14" s="20">
+        <v>0</v>
+      </c>
+      <c r="K14" s="20">
+        <v>0</v>
+      </c>
+      <c r="L14" s="20">
+        <v>0</v>
+      </c>
+      <c r="M14" s="20">
+        <v>0</v>
+      </c>
+      <c r="N14" s="20">
+        <v>0</v>
+      </c>
+      <c r="O14" s="20">
+        <v>0</v>
+      </c>
+      <c r="P14" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="20">
+        <v>0</v>
+      </c>
+      <c r="R14" s="20">
+        <v>0</v>
+      </c>
+      <c r="S14" s="20">
+        <v>0</v>
+      </c>
+      <c r="T14" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U14" s="1">
-        <v>0</v>
-      </c>
-      <c r="V14" s="1">
-        <v>0</v>
-      </c>
-      <c r="W14" s="1">
-        <v>0</v>
-      </c>
-      <c r="X14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="19">
+      <c r="U14" s="20">
+        <v>0</v>
+      </c>
+      <c r="V14" s="20">
+        <v>0</v>
+      </c>
+      <c r="W14" s="20">
+        <v>0</v>
+      </c>
+      <c r="X14" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="29">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="29">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="29">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="29">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="29">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
+      <c r="A15" s="20">
         <v>10</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="1" t="s">
+      <c r="B15" s="1"/>
+      <c r="C15" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-      <c r="P15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
-      <c r="S15" s="1">
-        <v>0</v>
-      </c>
-      <c r="T15" s="1">
+      <c r="D15" s="20">
+        <v>0</v>
+      </c>
+      <c r="E15" s="20">
+        <v>0</v>
+      </c>
+      <c r="F15" s="20">
+        <v>0</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0</v>
+      </c>
+      <c r="H15" s="20">
+        <v>0</v>
+      </c>
+      <c r="I15" s="20">
+        <v>0</v>
+      </c>
+      <c r="J15" s="20">
+        <v>0</v>
+      </c>
+      <c r="K15" s="20">
+        <v>0</v>
+      </c>
+      <c r="L15" s="20">
+        <v>0</v>
+      </c>
+      <c r="M15" s="20">
+        <v>0</v>
+      </c>
+      <c r="N15" s="20">
+        <v>0</v>
+      </c>
+      <c r="O15" s="20">
+        <v>0</v>
+      </c>
+      <c r="P15" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="20">
+        <v>0</v>
+      </c>
+      <c r="R15" s="20">
+        <v>0</v>
+      </c>
+      <c r="S15" s="20">
+        <v>0</v>
+      </c>
+      <c r="T15" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U15" s="1">
-        <v>0</v>
-      </c>
-      <c r="V15" s="1">
-        <v>0</v>
-      </c>
-      <c r="W15" s="1">
-        <v>0</v>
-      </c>
-      <c r="X15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="19">
+      <c r="U15" s="20">
+        <v>0</v>
+      </c>
+      <c r="V15" s="20">
+        <v>0</v>
+      </c>
+      <c r="W15" s="20">
+        <v>0</v>
+      </c>
+      <c r="X15" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="29">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="29">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="29">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="29">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="29">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
+      <c r="A16" s="20">
         <v>11</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="1" t="s">
+      <c r="B16" s="1"/>
+      <c r="C16" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>0</v>
-      </c>
-      <c r="R16" s="1">
-        <v>0</v>
-      </c>
-      <c r="S16" s="1">
-        <v>0</v>
-      </c>
-      <c r="T16" s="1">
+      <c r="D16" s="20">
+        <v>0</v>
+      </c>
+      <c r="E16" s="20">
+        <v>0</v>
+      </c>
+      <c r="F16" s="20">
+        <v>0</v>
+      </c>
+      <c r="G16" s="20">
+        <v>0</v>
+      </c>
+      <c r="H16" s="20">
+        <v>0</v>
+      </c>
+      <c r="I16" s="20">
+        <v>0</v>
+      </c>
+      <c r="J16" s="20">
+        <v>0</v>
+      </c>
+      <c r="K16" s="20">
+        <v>0</v>
+      </c>
+      <c r="L16" s="20">
+        <v>0</v>
+      </c>
+      <c r="M16" s="20">
+        <v>0</v>
+      </c>
+      <c r="N16" s="20">
+        <v>0</v>
+      </c>
+      <c r="O16" s="20">
+        <v>0</v>
+      </c>
+      <c r="P16" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="20">
+        <v>0</v>
+      </c>
+      <c r="R16" s="20">
+        <v>0</v>
+      </c>
+      <c r="S16" s="20">
+        <v>0</v>
+      </c>
+      <c r="T16" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U16" s="1">
-        <v>0</v>
-      </c>
-      <c r="V16" s="1">
-        <v>0</v>
-      </c>
-      <c r="W16" s="1">
-        <v>0</v>
-      </c>
-      <c r="X16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="19">
+      <c r="U16" s="20">
+        <v>0</v>
+      </c>
+      <c r="V16" s="20">
+        <v>0</v>
+      </c>
+      <c r="W16" s="20">
+        <v>0</v>
+      </c>
+      <c r="X16" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="29">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="29">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="29">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="29">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="29">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:113" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
+      <c r="A17" s="20">
         <v>12</v>
       </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="1" t="s">
+      <c r="B17" s="1"/>
+      <c r="C17" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="1">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-      <c r="N17" s="1">
-        <v>0</v>
-      </c>
-      <c r="O17" s="1">
-        <v>0</v>
-      </c>
-      <c r="P17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>0</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-      <c r="S17" s="1">
-        <v>0</v>
-      </c>
-      <c r="T17" s="1">
+      <c r="D17" s="20">
+        <v>0</v>
+      </c>
+      <c r="E17" s="20">
+        <v>0</v>
+      </c>
+      <c r="F17" s="20">
+        <v>0</v>
+      </c>
+      <c r="G17" s="20">
+        <v>0</v>
+      </c>
+      <c r="H17" s="20">
+        <v>0</v>
+      </c>
+      <c r="I17" s="20">
+        <v>0</v>
+      </c>
+      <c r="J17" s="20">
+        <v>0</v>
+      </c>
+      <c r="K17" s="20">
+        <v>0</v>
+      </c>
+      <c r="L17" s="20">
+        <v>0</v>
+      </c>
+      <c r="M17" s="20">
+        <v>0</v>
+      </c>
+      <c r="N17" s="20">
+        <v>0</v>
+      </c>
+      <c r="O17" s="20">
+        <v>0</v>
+      </c>
+      <c r="P17" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="20">
+        <v>0</v>
+      </c>
+      <c r="R17" s="20">
+        <v>0</v>
+      </c>
+      <c r="S17" s="20">
+        <v>0</v>
+      </c>
+      <c r="T17" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U17" s="1">
-        <v>0</v>
-      </c>
-      <c r="V17" s="1">
-        <v>0</v>
-      </c>
-      <c r="W17" s="1">
-        <v>0</v>
-      </c>
-      <c r="X17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="19">
+      <c r="U17" s="20">
+        <v>0</v>
+      </c>
+      <c r="V17" s="20">
+        <v>0</v>
+      </c>
+      <c r="W17" s="20">
+        <v>0</v>
+      </c>
+      <c r="X17" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="29">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="29">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="29">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="29">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="29">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:113" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
+      <c r="A18" s="20">
         <v>13</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="1" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0</v>
-      </c>
-      <c r="F18" s="1">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1">
-        <v>0</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0</v>
-      </c>
-      <c r="P18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>0</v>
-      </c>
-      <c r="R18" s="1">
-        <v>0</v>
-      </c>
-      <c r="S18" s="1">
-        <v>0</v>
-      </c>
-      <c r="T18" s="1">
+      <c r="D18" s="20">
+        <v>0</v>
+      </c>
+      <c r="E18" s="20">
+        <v>0</v>
+      </c>
+      <c r="F18" s="20">
+        <v>0</v>
+      </c>
+      <c r="G18" s="20">
+        <v>0</v>
+      </c>
+      <c r="H18" s="20">
+        <v>0</v>
+      </c>
+      <c r="I18" s="20">
+        <v>0</v>
+      </c>
+      <c r="J18" s="20">
+        <v>0</v>
+      </c>
+      <c r="K18" s="20">
+        <v>0</v>
+      </c>
+      <c r="L18" s="20">
+        <v>0</v>
+      </c>
+      <c r="M18" s="20">
+        <v>0</v>
+      </c>
+      <c r="N18" s="20">
+        <v>0</v>
+      </c>
+      <c r="O18" s="20">
+        <v>0</v>
+      </c>
+      <c r="P18" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="20">
+        <v>0</v>
+      </c>
+      <c r="R18" s="20">
+        <v>0</v>
+      </c>
+      <c r="S18" s="20">
+        <v>0</v>
+      </c>
+      <c r="T18" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U18" s="1">
-        <v>0</v>
-      </c>
-      <c r="V18" s="1">
-        <v>0</v>
-      </c>
-      <c r="W18" s="1">
-        <v>0</v>
-      </c>
-      <c r="X18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="19">
+      <c r="U18" s="20">
+        <v>0</v>
+      </c>
+      <c r="V18" s="20">
+        <v>0</v>
+      </c>
+      <c r="W18" s="20">
+        <v>0</v>
+      </c>
+      <c r="X18" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="29">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="29">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="29">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="29">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="29">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13" t="s">
+      <c r="B19" s="21"/>
+      <c r="C19" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="22">
         <f t="shared" ref="D19:AG19" si="1">SUM(D5:D16)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M19" s="14">
+      <c r="M19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N19" s="14">
+      <c r="N19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O19" s="14">
+      <c r="O19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P19" s="14">
+      <c r="P19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="14">
+      <c r="Q19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R19" s="14">
+      <c r="R19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S19" s="14">
+      <c r="S19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T19" s="14">
+      <c r="T19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U19" s="14">
+      <c r="U19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V19" s="14">
+      <c r="V19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W19" s="14">
+      <c r="W19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X19" s="14">
+      <c r="X19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y19" s="14">
+      <c r="Y19" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z19" s="15">
+      <c r="Z19" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="15">
+      <c r="AA19" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB19" s="15">
+      <c r="AB19" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC19" s="15">
+      <c r="AC19" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD19" s="15">
+      <c r="AD19" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE19" s="15">
+      <c r="AE19" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF19" s="15">
+      <c r="AF19" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG19" s="15">
+      <c r="AG19" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13" t="s">
+      <c r="B20" s="21"/>
+      <c r="C20" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="22">
         <f t="shared" ref="D20:AG20" si="2">SUM(D6:D19)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M20" s="14">
+      <c r="M20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N20" s="14">
+      <c r="N20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O20" s="14">
+      <c r="O20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P20" s="14">
+      <c r="P20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="14">
+      <c r="Q20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R20" s="14">
+      <c r="R20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S20" s="14">
+      <c r="S20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T20" s="14">
+      <c r="T20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U20" s="14">
+      <c r="U20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V20" s="14">
+      <c r="V20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W20" s="14">
+      <c r="W20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X20" s="14">
+      <c r="X20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y20" s="14">
+      <c r="Y20" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z20" s="28">
+      <c r="Z20" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="28">
+      <c r="AA20" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AB20" s="28">
+      <c r="AB20" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC20" s="28">
+      <c r="AC20" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD20" s="28">
+      <c r="AD20" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AE20" s="28">
+      <c r="AE20" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AF20" s="28">
+      <c r="AF20" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="28">
+      <c r="AG20" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:113" x14ac:dyDescent="0.2">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="17" t="s">
+      <c r="B21" s="25"/>
+      <c r="C21" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="22">
         <f t="shared" ref="D21:AD21" si="3">D19-D20</f>
         <v>0</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L21" s="14">
+      <c r="L21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M21" s="14">
+      <c r="M21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N21" s="14">
+      <c r="N21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O21" s="14">
+      <c r="O21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P21" s="14">
+      <c r="P21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="14">
+      <c r="Q21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R21" s="14">
+      <c r="R21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S21" s="14">
+      <c r="S21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T21" s="14">
+      <c r="T21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U21" s="14">
+      <c r="U21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V21" s="14">
+      <c r="V21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W21" s="14">
+      <c r="W21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X21" s="18">
+      <c r="X21" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y21" s="14">
+      <c r="Y21" s="22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z21" s="15">
+      <c r="Z21" s="23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA21" s="15">
+      <c r="AA21" s="23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB21" s="15">
+      <c r="AB21" s="23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC21" s="15">
+      <c r="AC21" s="23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AD21" s="15">
+      <c r="AD21" s="23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE21" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="15">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="15">
-        <v>0</v>
-      </c>
+      <c r="AE21" s="28"/>
+      <c r="AF21" s="23"/>
+      <c r="AG21" s="23"/>
     </row>
-    <row r="22" spans="1:113" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="Z22" s="5"/>
-      <c r="AA22" s="5"/>
-      <c r="AB22" s="5"/>
-      <c r="AC22" s="5"/>
-      <c r="AD22" s="5"/>
-      <c r="AE22" s="5"/>
-      <c r="AF22" s="5"/>
-      <c r="AG22" s="5"/>
+    <row r="22" spans="1:113" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="9"/>
+      <c r="AG22" s="9"/>
       <c r="AH22"/>
       <c r="AI22"/>
       <c r="AJ22"/>
@@ -2824,16 +2821,16 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:K2"/>
-    <mergeCell ref="L2:S2"/>
-    <mergeCell ref="T2:T4"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="Y2:Y4"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AE3:AE4"/>
     <mergeCell ref="Z2:AA2"/>
     <mergeCell ref="AB2:AC2"/>
     <mergeCell ref="AD2:AD4"/>
@@ -2850,16 +2847,16 @@
     <mergeCell ref="V3:V4"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:K2"/>
+    <mergeCell ref="L2:S2"/>
+    <mergeCell ref="T2:T4"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="Y2:Y4"/>
   </mergeCells>
   <conditionalFormatting sqref="AD8:AG8">
     <cfRule type="dataBar" priority="3">
